--- a/xlsx/技能/闪现.xlsx
+++ b/xlsx/技能/闪现.xlsx
@@ -36,9 +36,6 @@
     for (let datum of data) {
         if (datum.id) {
             let actorType = ActorTypeUtil.registerActorType(datum as any);
-   actorType.onAction = (actor, x, y, targetUnit)=&gt;{
-    UnitUtil.transfer(actor.unit,x,y)
-   }
         }
     }
 %&gt;</t>
